--- a/MI_final.xlsx
+++ b/MI_final.xlsx
@@ -669,106 +669,106 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>110542011.9</v>
+        <v>112858119.81</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>62633334.5</v>
+        <v>63962949.58</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>76355441.89</v>
+        <v>77698459.14</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>55107666.78</v>
+        <v>56188436.39</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46233989.86</v>
+        <v>47146060.85</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>41855996.62</v>
+        <v>42414211.48</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>32920119.64</v>
+        <v>33333286.96</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>36452293.05</v>
+        <v>37020886.4</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>78160908.37</v>
+        <v>79431984.76000001</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>80102365.38</v>
+        <v>81467269.33999999</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>77800499.86</v>
+        <v>79805788.61</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>76651619.47</v>
+        <v>78515413.25</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>73202772.48</v>
+        <v>74930495.46000001</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>58712208.64</v>
+        <v>60204015.18</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>65966199.37</v>
+        <v>67631452.39999999</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>58138707.82</v>
+        <v>59537707.3</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>46911871.17</v>
+        <v>48066463.93</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>40483598.47</v>
+        <v>41210564.89</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>33603152.43</v>
+        <v>34212802.03</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>41205758.13</v>
+        <v>42084654.47000001</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>74788298.84999999</v>
+        <v>76465210</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>84339704.5</v>
+        <v>85999606.27</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>93780440.41</v>
+        <v>96210101.03999999</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>85895327.5</v>
+        <v>87708096.45</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>76202716.45999999</v>
+        <v>78039367.89999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>54741640.77</v>
+        <v>56520536.99</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>69950654.5</v>
+        <v>71667931.51000001</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>53896159.27</v>
+        <v>55360661.89</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>54736713.59</v>
+        <v>55819019.12</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>40935275.43</v>
+        <v>41564660.71</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>36889890.02</v>
+        <v>37427585.81</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>50748837.14</v>
+        <v>51951288.81</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>66724941.25</v>
+        <v>70100588.09999999</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>70532170.06999999</v>
+        <v>73791240.88</v>
       </c>
     </row>
     <row r="3">
@@ -2435,106 +2435,106 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3404669.460000008</v>
+        <v>3345917.280000008</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3121738.310000002</v>
+        <v>3150874.160000002</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9721420.07</v>
+        <v>9856638.359999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6355614.859999999</v>
+        <v>6387208.199999999</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6324215.780000001</v>
+        <v>6300996.790000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2934943.140000001</v>
+        <v>2964360.210000001</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>4114831.84</v>
+        <v>4155099.01</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3667518.729999997</v>
+        <v>3698719.529999997</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7797491.090000004</v>
+        <v>7888445.820000004</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>6897742.349999994</v>
+        <v>6928293.609999994</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>4507461.370000005</v>
+        <v>4539370.660000005</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8627334.709999993</v>
+        <v>8704891.459999993</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>5829206.960000008</v>
+        <v>5982622.500000008</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>3611388.060000002</v>
+        <v>3534588.870000002</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>6104030.029999994</v>
+        <v>6106505.099999994</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>5668847.549999997</v>
+        <v>5752647.219999997</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>5468188.5</v>
+        <v>5498555.310000001</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>3617038.939999998</v>
+        <v>3691990.959999998</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>4063710.140000001</v>
+        <v>4128116.070000001</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>4643822.400000006</v>
+        <v>4636429.050000006</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>9293137.739999995</v>
+        <v>9293682.379999995</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>4646185.680000007</v>
+        <v>4691146.450000007</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>9659311.649999991</v>
+        <v>9686349.209999992</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>3154697.430000007</v>
+        <v>3171555.360000007</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>10281961.00999999</v>
+        <v>10270066.61999999</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>4910625.010000005</v>
+        <v>4911279.630000005</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>3892522.829999998</v>
+        <v>3932980.919999998</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>5802186.340000004</v>
+        <v>5859553.900000004</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>7421774.330000006</v>
+        <v>7470022.750000006</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>5365818.399999999</v>
+        <v>5333903.05</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>5208774.740000002</v>
+        <v>5255587.480000002</v>
       </c>
       <c r="AG2" s="2" t="n">
-        <v>6771134.840000004</v>
+        <v>6847730.240000004</v>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>6835635.159999996</v>
+        <v>6906398.419999996</v>
       </c>
       <c r="AI2" s="2" t="n">
-        <v>10658931.95999999</v>
+        <v>10852293.79999999</v>
       </c>
     </row>
     <row r="3">
@@ -4201,106 +4201,106 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.03079977830582625</v>
+        <v>0.02964711166226196</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.0498414835314253</v>
+        <v>0.04926092653152475</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.1273179727517651</v>
+        <v>0.1268575782466926</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.1153308646757408</v>
+        <v>0.1136747809756946</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1367871515988605</v>
+        <v>0.1336484252639317</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.0701200156968094</v>
+        <v>0.06989073017183912</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.1249944375961569</v>
+        <v>0.1246531437174535</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.1006114683915611</v>
+        <v>0.09990899434541894</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.09976203261466782</v>
+        <v>0.09931069762180274</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.08611159379972849</v>
+        <v>0.08504389144412183</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.0579361492292603</v>
+        <v>0.05688021807770473</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0.1125525431772067</v>
+        <v>0.1108685683444453</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0.07963095880818759</v>
+        <v>0.07984229202372883</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>0.06151000181484574</v>
+        <v>0.05871018501726452</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.09253269232266813</v>
+        <v>0.09029090583303805</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.09750556492502377</v>
+        <v>0.09662191375649423</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.1165630012962879</v>
+        <v>0.1143948370740906</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>0.08934578636037929</v>
+        <v>0.0895884579562238</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0.1209324080074115</v>
+        <v>0.1206599817922017</v>
       </c>
       <c r="U2" s="3" t="n">
-        <v>0.112698385146785</v>
+        <v>0.1101691129080097</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>0.1242592475413685</v>
+        <v>0.121541317678981</v>
       </c>
       <c r="W2" s="3" t="n">
-        <v>0.05508894900147542</v>
+        <v>0.05454846427170749</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>0.1029992139914284</v>
+        <v>0.1006791293772036</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>0.03672722977859311</v>
+        <v>0.03616034879753689</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>0.1349290614252204</v>
+        <v>0.1316010995009609</v>
       </c>
       <c r="AA2" s="3" t="n">
-        <v>0.08970547723683082</v>
+        <v>0.08689371848800627</v>
       </c>
       <c r="AB2" s="3" t="n">
-        <v>0.05564669634363462</v>
+        <v>0.05487783499725005</v>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>0.1076549130510984</v>
+        <v>0.105843277517938</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>0.1355904263012953</v>
+        <v>0.1338257616806364</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.1310805495660005</v>
+        <v>0.1283278380934004</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>0.1411978928962934</v>
+        <v>0.1404201571183306</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>0.1334244333780611</v>
+        <v>0.1318105940555973</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>0.1024449783236039</v>
+        <v>0.09852126219180744</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>0.1511215655128927</v>
+        <v>0.1470675065303224</v>
       </c>
     </row>
     <row r="3">
